--- a/5/search/FY4_Missile1_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY4_Missile1_results/fine_tuned/comparison.xlsx
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>315.8</v>
+        <v>315</v>
       </c>
       <c r="C3" t="n">
-        <v>131.3</v>
+        <v>131.8</v>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.600000000000001</v>
+        <v>1.799999999999997</v>
       </c>
     </row>
   </sheetData>
